--- a/data.mn/public/datasets/weekly-fuel-prices-ulaanbaatar.xlsx
+++ b/data.mn/public/datasets/weekly-fuel-prices-ulaanbaatar.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D288"/>
+  <dimension ref="A1:D296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4993,6 +4993,118 @@
       <c r="C288" t="inlineStr"/>
       <c r="D288" t="n">
         <v>3040</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>4770</v>
+      </c>
+      <c r="C289" t="inlineStr"/>
+      <c r="D289" t="n">
+        <v>3040</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>4770</v>
+      </c>
+      <c r="C290" t="inlineStr"/>
+      <c r="D290" t="n">
+        <v>3040</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>4770</v>
+      </c>
+      <c r="C291" t="inlineStr"/>
+      <c r="D291" t="n">
+        <v>3040</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>4775</v>
+      </c>
+      <c r="C292" t="inlineStr"/>
+      <c r="D292" t="n">
+        <v>3040</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>4775</v>
+      </c>
+      <c r="C293" t="inlineStr"/>
+      <c r="D293" t="n">
+        <v>3040</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>4775</v>
+      </c>
+      <c r="C294" t="inlineStr"/>
+      <c r="D294" t="n">
+        <v>3592</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>4775</v>
+      </c>
+      <c r="C295" t="inlineStr"/>
+      <c r="D295" t="n">
+        <v>3592</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>5700</v>
+      </c>
+      <c r="C296" t="inlineStr"/>
+      <c r="D296" t="n">
+        <v>3592</v>
       </c>
     </row>
   </sheetData>
@@ -5006,13 +5118,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D288"/>
+  <dimension ref="A1:D296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5023,17 +5135,17 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Дизелийн түлш, л</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Аи-80 автобензин, л</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Аи-92 автобензин, л</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Дизелийн түлш, л</t>
         </is>
       </c>
     </row>
@@ -5044,13 +5156,13 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>2040</v>
+      </c>
+      <c r="C2" t="n">
         <v>1349</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>1422</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2040</v>
       </c>
     </row>
     <row r="3">
@@ -5060,13 +5172,13 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>2040</v>
+      </c>
+      <c r="C3" t="n">
         <v>1349</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>1422</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2040</v>
       </c>
     </row>
     <row r="4">
@@ -5076,13 +5188,13 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>2040</v>
+      </c>
+      <c r="C4" t="n">
         <v>1349</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>1428</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2040</v>
       </c>
     </row>
     <row r="5">
@@ -5092,13 +5204,13 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>2040</v>
+      </c>
+      <c r="C5" t="n">
         <v>1349</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>1428</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2040</v>
       </c>
     </row>
     <row r="6">
@@ -5108,13 +5220,13 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>2063</v>
+      </c>
+      <c r="C6" t="n">
         <v>1349</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>1434</v>
-      </c>
-      <c r="D6" t="n">
-        <v>2063</v>
       </c>
     </row>
     <row r="7">
@@ -5124,13 +5236,13 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>2063</v>
+      </c>
+      <c r="C7" t="n">
         <v>1349</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>1434</v>
-      </c>
-      <c r="D7" t="n">
-        <v>2063</v>
       </c>
     </row>
     <row r="8">
@@ -5140,13 +5252,13 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>2063</v>
+      </c>
+      <c r="C8" t="n">
         <v>1349</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>1434</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2063</v>
       </c>
     </row>
     <row r="9">
@@ -5156,13 +5268,13 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>2122</v>
+      </c>
+      <c r="C9" t="n">
         <v>1349</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>1434</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2122</v>
       </c>
     </row>
     <row r="10">
@@ -5172,13 +5284,13 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>2142</v>
+      </c>
+      <c r="C10" t="n">
         <v>1349</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>1434</v>
-      </c>
-      <c r="D10" t="n">
-        <v>2142</v>
       </c>
     </row>
     <row r="11">
@@ -5188,13 +5300,13 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>2142</v>
+      </c>
+      <c r="C11" t="n">
         <v>1349</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>1434</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2142</v>
       </c>
     </row>
     <row r="12">
@@ -5204,13 +5316,13 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>2142</v>
+      </c>
+      <c r="C12" t="n">
         <v>1349</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>1434</v>
-      </c>
-      <c r="D12" t="n">
-        <v>2142</v>
       </c>
     </row>
     <row r="13">
@@ -5220,13 +5332,13 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>2142</v>
+      </c>
+      <c r="C13" t="n">
         <v>1349</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>1434</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2142</v>
       </c>
     </row>
     <row r="14">
@@ -5236,13 +5348,13 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>2142</v>
+      </c>
+      <c r="C14" t="n">
         <v>1349</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>1434</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2142</v>
       </c>
     </row>
     <row r="15">
@@ -5252,13 +5364,13 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>2142</v>
+      </c>
+      <c r="C15" t="n">
         <v>1349</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>1434</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2142</v>
       </c>
     </row>
     <row r="16">
@@ -5268,13 +5380,13 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>2142</v>
+      </c>
+      <c r="C16" t="n">
         <v>1349</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>1434</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2142</v>
       </c>
     </row>
     <row r="17">
@@ -5284,13 +5396,13 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>2142</v>
+      </c>
+      <c r="C17" t="n">
         <v>1349</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>1434</v>
-      </c>
-      <c r="D17" t="n">
-        <v>2142</v>
       </c>
     </row>
     <row r="18">
@@ -5300,13 +5412,13 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>2142</v>
+      </c>
+      <c r="C18" t="n">
         <v>1349</v>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>1434</v>
-      </c>
-      <c r="D18" t="n">
-        <v>2142</v>
       </c>
     </row>
     <row r="19">
@@ -5316,13 +5428,13 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>2220</v>
+      </c>
+      <c r="C19" t="n">
         <v>1349</v>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
         <v>1434</v>
-      </c>
-      <c r="D19" t="n">
-        <v>2220</v>
       </c>
     </row>
     <row r="20">
@@ -5332,13 +5444,13 @@
         </is>
       </c>
       <c r="B20" t="n">
+        <v>2227</v>
+      </c>
+      <c r="C20" t="n">
         <v>1385</v>
       </c>
-      <c r="C20" t="n">
+      <c r="D20" t="n">
         <v>1450</v>
-      </c>
-      <c r="D20" t="n">
-        <v>2227</v>
       </c>
     </row>
     <row r="21">
@@ -5348,13 +5460,13 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>2227</v>
+      </c>
+      <c r="C21" t="n">
         <v>1385</v>
       </c>
-      <c r="C21" t="n">
+      <c r="D21" t="n">
         <v>1450</v>
-      </c>
-      <c r="D21" t="n">
-        <v>2227</v>
       </c>
     </row>
     <row r="22">
@@ -5364,13 +5476,13 @@
         </is>
       </c>
       <c r="B22" t="n">
+        <v>2227</v>
+      </c>
+      <c r="C22" t="n">
         <v>1385</v>
       </c>
-      <c r="C22" t="n">
+      <c r="D22" t="n">
         <v>1450</v>
-      </c>
-      <c r="D22" t="n">
-        <v>2227</v>
       </c>
     </row>
     <row r="23">
@@ -5380,13 +5492,13 @@
         </is>
       </c>
       <c r="B23" t="n">
+        <v>2227</v>
+      </c>
+      <c r="C23" t="n">
         <v>1385</v>
       </c>
-      <c r="C23" t="n">
+      <c r="D23" t="n">
         <v>1450</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2227</v>
       </c>
     </row>
     <row r="24">
@@ -5396,13 +5508,13 @@
         </is>
       </c>
       <c r="B24" t="n">
+        <v>2227</v>
+      </c>
+      <c r="C24" t="n">
         <v>1385</v>
       </c>
-      <c r="C24" t="n">
+      <c r="D24" t="n">
         <v>1450</v>
-      </c>
-      <c r="D24" t="n">
-        <v>2227</v>
       </c>
     </row>
     <row r="25">
@@ -5412,13 +5524,13 @@
         </is>
       </c>
       <c r="B25" t="n">
+        <v>2227</v>
+      </c>
+      <c r="C25" t="n">
         <v>1385</v>
       </c>
-      <c r="C25" t="n">
+      <c r="D25" t="n">
         <v>1450</v>
-      </c>
-      <c r="D25" t="n">
-        <v>2227</v>
       </c>
     </row>
     <row r="26">
@@ -5428,13 +5540,13 @@
         </is>
       </c>
       <c r="B26" t="n">
+        <v>2227</v>
+      </c>
+      <c r="C26" t="n">
         <v>1385</v>
       </c>
-      <c r="C26" t="n">
+      <c r="D26" t="n">
         <v>1450</v>
-      </c>
-      <c r="D26" t="n">
-        <v>2227</v>
       </c>
     </row>
     <row r="27">
@@ -5444,13 +5556,13 @@
         </is>
       </c>
       <c r="B27" t="n">
+        <v>2261</v>
+      </c>
+      <c r="C27" t="n">
         <v>1385</v>
       </c>
-      <c r="C27" t="n">
+      <c r="D27" t="n">
         <v>1450</v>
-      </c>
-      <c r="D27" t="n">
-        <v>2261</v>
       </c>
     </row>
     <row r="28">
@@ -5460,13 +5572,13 @@
         </is>
       </c>
       <c r="B28" t="n">
+        <v>2361</v>
+      </c>
+      <c r="C28" t="n">
         <v>1690</v>
       </c>
-      <c r="C28" t="n">
+      <c r="D28" t="n">
         <v>1744</v>
-      </c>
-      <c r="D28" t="n">
-        <v>2361</v>
       </c>
     </row>
     <row r="29">
@@ -5476,13 +5588,13 @@
         </is>
       </c>
       <c r="B29" t="n">
+        <v>2361</v>
+      </c>
+      <c r="C29" t="n">
         <v>1690</v>
       </c>
-      <c r="C29" t="n">
+      <c r="D29" t="n">
         <v>1744</v>
-      </c>
-      <c r="D29" t="n">
-        <v>2361</v>
       </c>
     </row>
     <row r="30">
@@ -5492,13 +5604,13 @@
         </is>
       </c>
       <c r="B30" t="n">
+        <v>2361</v>
+      </c>
+      <c r="C30" t="n">
         <v>1690</v>
       </c>
-      <c r="C30" t="n">
+      <c r="D30" t="n">
         <v>1744</v>
-      </c>
-      <c r="D30" t="n">
-        <v>2361</v>
       </c>
     </row>
     <row r="31">
@@ -5508,13 +5620,13 @@
         </is>
       </c>
       <c r="B31" t="n">
+        <v>2361</v>
+      </c>
+      <c r="C31" t="n">
         <v>1690</v>
       </c>
-      <c r="C31" t="n">
+      <c r="D31" t="n">
         <v>1744</v>
-      </c>
-      <c r="D31" t="n">
-        <v>2361</v>
       </c>
     </row>
     <row r="32">
@@ -5524,13 +5636,13 @@
         </is>
       </c>
       <c r="B32" t="n">
+        <v>2459</v>
+      </c>
+      <c r="C32" t="n">
         <v>1970</v>
       </c>
-      <c r="C32" t="n">
+      <c r="D32" t="n">
         <v>2036</v>
-      </c>
-      <c r="D32" t="n">
-        <v>2459</v>
       </c>
     </row>
     <row r="33">
@@ -5540,13 +5652,13 @@
         </is>
       </c>
       <c r="B33" t="n">
+        <v>2459</v>
+      </c>
+      <c r="C33" t="n">
         <v>1970</v>
       </c>
-      <c r="C33" t="n">
+      <c r="D33" t="n">
         <v>2036</v>
-      </c>
-      <c r="D33" t="n">
-        <v>2459</v>
       </c>
     </row>
     <row r="34">
@@ -5556,13 +5668,13 @@
         </is>
       </c>
       <c r="B34" t="n">
+        <v>2459</v>
+      </c>
+      <c r="C34" t="n">
         <v>1970</v>
       </c>
-      <c r="C34" t="n">
+      <c r="D34" t="n">
         <v>2036</v>
-      </c>
-      <c r="D34" t="n">
-        <v>2459</v>
       </c>
     </row>
     <row r="35">
@@ -5572,13 +5684,13 @@
         </is>
       </c>
       <c r="B35" t="n">
+        <v>2459</v>
+      </c>
+      <c r="C35" t="n">
         <v>1970</v>
       </c>
-      <c r="C35" t="n">
+      <c r="D35" t="n">
         <v>2036</v>
-      </c>
-      <c r="D35" t="n">
-        <v>2459</v>
       </c>
     </row>
     <row r="36">
@@ -5588,13 +5700,13 @@
         </is>
       </c>
       <c r="B36" t="n">
+        <v>2459</v>
+      </c>
+      <c r="C36" t="n">
         <v>1970</v>
       </c>
-      <c r="C36" t="n">
+      <c r="D36" t="n">
         <v>2036</v>
-      </c>
-      <c r="D36" t="n">
-        <v>2459</v>
       </c>
     </row>
     <row r="37">
@@ -5604,13 +5716,13 @@
         </is>
       </c>
       <c r="B37" t="n">
+        <v>2459</v>
+      </c>
+      <c r="C37" t="n">
         <v>1970</v>
       </c>
-      <c r="C37" t="n">
+      <c r="D37" t="n">
         <v>2036</v>
-      </c>
-      <c r="D37" t="n">
-        <v>2459</v>
       </c>
     </row>
     <row r="38">
@@ -5620,13 +5732,13 @@
         </is>
       </c>
       <c r="B38" t="n">
+        <v>2459</v>
+      </c>
+      <c r="C38" t="n">
         <v>1970</v>
       </c>
-      <c r="C38" t="n">
+      <c r="D38" t="n">
         <v>2036</v>
-      </c>
-      <c r="D38" t="n">
-        <v>2459</v>
       </c>
     </row>
     <row r="39">
@@ -5636,13 +5748,13 @@
         </is>
       </c>
       <c r="B39" t="n">
+        <v>2459</v>
+      </c>
+      <c r="C39" t="n">
         <v>1970</v>
       </c>
-      <c r="C39" t="n">
+      <c r="D39" t="n">
         <v>2036</v>
-      </c>
-      <c r="D39" t="n">
-        <v>2459</v>
       </c>
     </row>
     <row r="40">
@@ -5652,13 +5764,13 @@
         </is>
       </c>
       <c r="B40" t="n">
+        <v>2459</v>
+      </c>
+      <c r="C40" t="n">
         <v>1970</v>
       </c>
-      <c r="C40" t="n">
+      <c r="D40" t="n">
         <v>2036</v>
-      </c>
-      <c r="D40" t="n">
-        <v>2459</v>
       </c>
     </row>
     <row r="41">
@@ -5668,13 +5780,13 @@
         </is>
       </c>
       <c r="B41" t="n">
+        <v>2459</v>
+      </c>
+      <c r="C41" t="n">
         <v>1970</v>
       </c>
-      <c r="C41" t="n">
+      <c r="D41" t="n">
         <v>2050</v>
-      </c>
-      <c r="D41" t="n">
-        <v>2459</v>
       </c>
     </row>
     <row r="42">
@@ -5684,13 +5796,13 @@
         </is>
       </c>
       <c r="B42" t="n">
+        <v>2459</v>
+      </c>
+      <c r="C42" t="n">
         <v>1970</v>
       </c>
-      <c r="C42" t="n">
+      <c r="D42" t="n">
         <v>2050</v>
-      </c>
-      <c r="D42" t="n">
-        <v>2459</v>
       </c>
     </row>
     <row r="43">
@@ -5700,13 +5812,13 @@
         </is>
       </c>
       <c r="B43" t="n">
+        <v>2518</v>
+      </c>
+      <c r="C43" t="n">
         <v>1970</v>
       </c>
-      <c r="C43" t="n">
+      <c r="D43" t="n">
         <v>2050</v>
-      </c>
-      <c r="D43" t="n">
-        <v>2518</v>
       </c>
     </row>
     <row r="44">
@@ -5716,13 +5828,13 @@
         </is>
       </c>
       <c r="B44" t="n">
+        <v>2557</v>
+      </c>
+      <c r="C44" t="n">
         <v>1970</v>
       </c>
-      <c r="C44" t="n">
+      <c r="D44" t="n">
         <v>2050</v>
-      </c>
-      <c r="D44" t="n">
-        <v>2557</v>
       </c>
     </row>
     <row r="45">
@@ -5732,13 +5844,13 @@
         </is>
       </c>
       <c r="B45" t="n">
+        <v>2616</v>
+      </c>
+      <c r="C45" t="n">
         <v>1970</v>
       </c>
-      <c r="C45" t="n">
+      <c r="D45" t="n">
         <v>2050</v>
-      </c>
-      <c r="D45" t="n">
-        <v>2616</v>
       </c>
     </row>
     <row r="46">
@@ -5748,13 +5860,13 @@
         </is>
       </c>
       <c r="B46" t="n">
+        <v>2658</v>
+      </c>
+      <c r="C46" t="n">
         <v>1970</v>
       </c>
-      <c r="C46" t="n">
+      <c r="D46" t="n">
         <v>2050</v>
-      </c>
-      <c r="D46" t="n">
-        <v>2658</v>
       </c>
     </row>
     <row r="47">
@@ -5764,13 +5876,13 @@
         </is>
       </c>
       <c r="B47" t="n">
+        <v>2757</v>
+      </c>
+      <c r="C47" t="n">
         <v>1970</v>
       </c>
-      <c r="C47" t="n">
+      <c r="D47" t="n">
         <v>2050</v>
-      </c>
-      <c r="D47" t="n">
-        <v>2757</v>
       </c>
     </row>
     <row r="48">
@@ -5780,13 +5892,13 @@
         </is>
       </c>
       <c r="B48" t="n">
+        <v>2776</v>
+      </c>
+      <c r="C48" t="n">
         <v>2033</v>
       </c>
-      <c r="C48" t="n">
+      <c r="D48" t="n">
         <v>2130</v>
-      </c>
-      <c r="D48" t="n">
-        <v>2776</v>
       </c>
     </row>
     <row r="49">
@@ -5796,13 +5908,13 @@
         </is>
       </c>
       <c r="B49" t="n">
+        <v>2776</v>
+      </c>
+      <c r="C49" t="n">
         <v>2033</v>
       </c>
-      <c r="C49" t="n">
+      <c r="D49" t="n">
         <v>2130</v>
-      </c>
-      <c r="D49" t="n">
-        <v>2776</v>
       </c>
     </row>
     <row r="50">
@@ -5812,13 +5924,13 @@
         </is>
       </c>
       <c r="B50" t="n">
+        <v>2855</v>
+      </c>
+      <c r="C50" t="n">
         <v>2100</v>
       </c>
-      <c r="C50" t="n">
+      <c r="D50" t="n">
         <v>2185</v>
-      </c>
-      <c r="D50" t="n">
-        <v>2855</v>
       </c>
     </row>
     <row r="51">
@@ -5828,13 +5940,13 @@
         </is>
       </c>
       <c r="B51" t="n">
+        <v>2890</v>
+      </c>
+      <c r="C51" t="n">
         <v>2200</v>
       </c>
-      <c r="C51" t="n">
+      <c r="D51" t="n">
         <v>2220</v>
-      </c>
-      <c r="D51" t="n">
-        <v>2890</v>
       </c>
     </row>
     <row r="52">
@@ -5844,13 +5956,13 @@
         </is>
       </c>
       <c r="B52" t="n">
+        <v>2890</v>
+      </c>
+      <c r="C52" t="n">
         <v>2200</v>
       </c>
-      <c r="C52" t="n">
+      <c r="D52" t="n">
         <v>2220</v>
-      </c>
-      <c r="D52" t="n">
-        <v>2890</v>
       </c>
     </row>
     <row r="53">
@@ -5860,13 +5972,13 @@
         </is>
       </c>
       <c r="B53" t="n">
+        <v>2900</v>
+      </c>
+      <c r="C53" t="n">
         <v>2200</v>
       </c>
-      <c r="C53" t="n">
+      <c r="D53" t="n">
         <v>2220</v>
-      </c>
-      <c r="D53" t="n">
-        <v>2900</v>
       </c>
     </row>
     <row r="54">
@@ -5876,13 +5988,13 @@
         </is>
       </c>
       <c r="B54" t="n">
+        <v>2920</v>
+      </c>
+      <c r="C54" t="n">
         <v>2200</v>
       </c>
-      <c r="C54" t="n">
+      <c r="D54" t="n">
         <v>2220</v>
-      </c>
-      <c r="D54" t="n">
-        <v>2920</v>
       </c>
     </row>
     <row r="55">
@@ -5892,13 +6004,13 @@
         </is>
       </c>
       <c r="B55" t="n">
+        <v>2890</v>
+      </c>
+      <c r="C55" t="n">
         <v>2220</v>
       </c>
-      <c r="C55" t="n">
+      <c r="D55" t="n">
         <v>2235</v>
-      </c>
-      <c r="D55" t="n">
-        <v>2890</v>
       </c>
     </row>
     <row r="56">
@@ -5908,13 +6020,13 @@
         </is>
       </c>
       <c r="B56" t="n">
+        <v>2870</v>
+      </c>
+      <c r="C56" t="n">
         <v>2220</v>
       </c>
-      <c r="C56" t="n">
+      <c r="D56" t="n">
         <v>2240</v>
-      </c>
-      <c r="D56" t="n">
-        <v>2870</v>
       </c>
     </row>
     <row r="57">
@@ -5924,13 +6036,13 @@
         </is>
       </c>
       <c r="B57" t="n">
+        <v>2870</v>
+      </c>
+      <c r="C57" t="n">
         <v>2220</v>
       </c>
-      <c r="C57" t="n">
+      <c r="D57" t="n">
         <v>2240</v>
-      </c>
-      <c r="D57" t="n">
-        <v>2870</v>
       </c>
     </row>
     <row r="58">
@@ -5940,13 +6052,13 @@
         </is>
       </c>
       <c r="B58" t="n">
+        <v>2860</v>
+      </c>
+      <c r="C58" t="n">
         <v>2270</v>
       </c>
-      <c r="C58" t="n">
+      <c r="D58" t="n">
         <v>2250</v>
-      </c>
-      <c r="D58" t="n">
-        <v>2860</v>
       </c>
     </row>
     <row r="59">
@@ -5956,13 +6068,13 @@
         </is>
       </c>
       <c r="B59" t="n">
+        <v>2860</v>
+      </c>
+      <c r="C59" t="n">
         <v>2270</v>
       </c>
-      <c r="C59" t="n">
+      <c r="D59" t="n">
         <v>2287</v>
-      </c>
-      <c r="D59" t="n">
-        <v>2860</v>
       </c>
     </row>
     <row r="60">
@@ -5972,13 +6084,13 @@
         </is>
       </c>
       <c r="B60" t="n">
+        <v>2907</v>
+      </c>
+      <c r="C60" t="n">
         <v>2270</v>
       </c>
-      <c r="C60" t="n">
+      <c r="D60" t="n">
         <v>2286</v>
-      </c>
-      <c r="D60" t="n">
-        <v>2907</v>
       </c>
     </row>
     <row r="61">
@@ -5988,13 +6100,13 @@
         </is>
       </c>
       <c r="B61" t="n">
+        <v>2932</v>
+      </c>
+      <c r="C61" t="n">
         <v>2270</v>
       </c>
-      <c r="C61" t="n">
+      <c r="D61" t="n">
         <v>2280</v>
-      </c>
-      <c r="D61" t="n">
-        <v>2932</v>
       </c>
     </row>
     <row r="62">
@@ -6004,13 +6116,13 @@
         </is>
       </c>
       <c r="B62" t="n">
+        <v>2932</v>
+      </c>
+      <c r="C62" t="n">
         <v>2370</v>
       </c>
-      <c r="C62" t="n">
+      <c r="D62" t="n">
         <v>2387</v>
-      </c>
-      <c r="D62" t="n">
-        <v>2932</v>
       </c>
     </row>
     <row r="63">
@@ -6020,13 +6132,13 @@
         </is>
       </c>
       <c r="B63" t="n">
+        <v>2932</v>
+      </c>
+      <c r="C63" t="n">
         <v>2370</v>
       </c>
-      <c r="C63" t="n">
+      <c r="D63" t="n">
         <v>2387</v>
-      </c>
-      <c r="D63" t="n">
-        <v>2932</v>
       </c>
     </row>
     <row r="64">
@@ -6036,13 +6148,13 @@
         </is>
       </c>
       <c r="B64" t="n">
+        <v>3131</v>
+      </c>
+      <c r="C64" t="n">
         <v>2370</v>
       </c>
-      <c r="C64" t="n">
+      <c r="D64" t="n">
         <v>2387</v>
-      </c>
-      <c r="D64" t="n">
-        <v>3131</v>
       </c>
     </row>
     <row r="65">
@@ -6052,13 +6164,13 @@
         </is>
       </c>
       <c r="B65" t="n">
+        <v>3131</v>
+      </c>
+      <c r="C65" t="n">
         <v>2370</v>
       </c>
-      <c r="C65" t="n">
+      <c r="D65" t="n">
         <v>2387</v>
-      </c>
-      <c r="D65" t="n">
-        <v>3131</v>
       </c>
     </row>
     <row r="66">
@@ -6068,13 +6180,13 @@
         </is>
       </c>
       <c r="B66" t="n">
+        <v>3131</v>
+      </c>
+      <c r="C66" t="n">
         <v>2370</v>
       </c>
-      <c r="C66" t="n">
+      <c r="D66" t="n">
         <v>2389</v>
-      </c>
-      <c r="D66" t="n">
-        <v>3131</v>
       </c>
     </row>
     <row r="67">
@@ -6084,13 +6196,13 @@
         </is>
       </c>
       <c r="B67" t="n">
+        <v>3131</v>
+      </c>
+      <c r="C67" t="n">
         <v>2370</v>
       </c>
-      <c r="C67" t="n">
+      <c r="D67" t="n">
         <v>2389</v>
-      </c>
-      <c r="D67" t="n">
-        <v>3131</v>
       </c>
     </row>
     <row r="68">
@@ -6100,13 +6212,13 @@
         </is>
       </c>
       <c r="B68" t="n">
+        <v>3380</v>
+      </c>
+      <c r="C68" t="n">
         <v>2370</v>
       </c>
-      <c r="C68" t="n">
+      <c r="D68" t="n">
         <v>2389</v>
-      </c>
-      <c r="D68" t="n">
-        <v>3380</v>
       </c>
     </row>
     <row r="69">
@@ -6116,13 +6228,13 @@
         </is>
       </c>
       <c r="B69" t="n">
+        <v>3380</v>
+      </c>
+      <c r="C69" t="n">
         <v>2370</v>
       </c>
-      <c r="C69" t="n">
+      <c r="D69" t="n">
         <v>2389</v>
-      </c>
-      <c r="D69" t="n">
-        <v>3380</v>
       </c>
     </row>
     <row r="70">
@@ -6132,13 +6244,13 @@
         </is>
       </c>
       <c r="B70" t="n">
+        <v>3380</v>
+      </c>
+      <c r="C70" t="n">
         <v>2370</v>
       </c>
-      <c r="C70" t="n">
+      <c r="D70" t="n">
         <v>2389</v>
-      </c>
-      <c r="D70" t="n">
-        <v>3380</v>
       </c>
     </row>
     <row r="71">
@@ -6148,13 +6260,13 @@
         </is>
       </c>
       <c r="B71" t="n">
+        <v>3380</v>
+      </c>
+      <c r="C71" t="n">
         <v>2370</v>
       </c>
-      <c r="C71" t="n">
+      <c r="D71" t="n">
         <v>2389</v>
-      </c>
-      <c r="D71" t="n">
-        <v>3380</v>
       </c>
     </row>
     <row r="72">
@@ -6164,13 +6276,13 @@
         </is>
       </c>
       <c r="B72" t="n">
+        <v>3380</v>
+      </c>
+      <c r="C72" t="n">
         <v>2370</v>
       </c>
-      <c r="C72" t="n">
+      <c r="D72" t="n">
         <v>2389</v>
-      </c>
-      <c r="D72" t="n">
-        <v>3380</v>
       </c>
     </row>
     <row r="73">
@@ -6180,13 +6292,13 @@
         </is>
       </c>
       <c r="B73" t="n">
+        <v>3430</v>
+      </c>
+      <c r="C73" t="n">
         <v>2370</v>
       </c>
-      <c r="C73" t="n">
-        <v>2390</v>
-      </c>
       <c r="D73" t="n">
-        <v>3430</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="74">
@@ -6196,13 +6308,13 @@
         </is>
       </c>
       <c r="B74" t="n">
+        <v>3430</v>
+      </c>
+      <c r="C74" t="n">
         <v>2370</v>
       </c>
-      <c r="C74" t="n">
+      <c r="D74" t="n">
         <v>2389</v>
-      </c>
-      <c r="D74" t="n">
-        <v>3430</v>
       </c>
     </row>
     <row r="75">
@@ -6212,13 +6324,13 @@
         </is>
       </c>
       <c r="B75" t="n">
+        <v>3455</v>
+      </c>
+      <c r="C75" t="n">
         <v>2370</v>
       </c>
-      <c r="C75" t="n">
+      <c r="D75" t="n">
         <v>2389</v>
-      </c>
-      <c r="D75" t="n">
-        <v>3455</v>
       </c>
     </row>
     <row r="76">
@@ -6228,13 +6340,13 @@
         </is>
       </c>
       <c r="B76" t="n">
+        <v>3455</v>
+      </c>
+      <c r="C76" t="n">
         <v>2370</v>
       </c>
-      <c r="C76" t="n">
+      <c r="D76" t="n">
         <v>2389</v>
-      </c>
-      <c r="D76" t="n">
-        <v>3455</v>
       </c>
     </row>
     <row r="77">
@@ -6244,13 +6356,13 @@
         </is>
       </c>
       <c r="B77" t="n">
+        <v>3730</v>
+      </c>
+      <c r="C77" t="n">
         <v>2370</v>
       </c>
-      <c r="C77" t="n">
+      <c r="D77" t="n">
         <v>2389</v>
-      </c>
-      <c r="D77" t="n">
-        <v>3730</v>
       </c>
     </row>
     <row r="78">
@@ -6260,13 +6372,13 @@
         </is>
       </c>
       <c r="B78" t="n">
+        <v>3730</v>
+      </c>
+      <c r="C78" t="n">
         <v>2370</v>
       </c>
-      <c r="C78" t="n">
+      <c r="D78" t="n">
         <v>2389</v>
-      </c>
-      <c r="D78" t="n">
-        <v>3730</v>
       </c>
     </row>
     <row r="79">
@@ -6276,13 +6388,13 @@
         </is>
       </c>
       <c r="B79" t="n">
+        <v>3730</v>
+      </c>
+      <c r="C79" t="n">
         <v>2370</v>
       </c>
-      <c r="C79" t="n">
+      <c r="D79" t="n">
         <v>2389</v>
-      </c>
-      <c r="D79" t="n">
-        <v>3730</v>
       </c>
     </row>
     <row r="80">
@@ -6292,13 +6404,13 @@
         </is>
       </c>
       <c r="B80" t="n">
+        <v>4030</v>
+      </c>
+      <c r="C80" t="n">
         <v>2370</v>
       </c>
-      <c r="C80" t="n">
+      <c r="D80" t="n">
         <v>2389</v>
-      </c>
-      <c r="D80" t="n">
-        <v>4030</v>
       </c>
     </row>
     <row r="81">
@@ -6308,13 +6420,13 @@
         </is>
       </c>
       <c r="B81" t="n">
+        <v>4030</v>
+      </c>
+      <c r="C81" t="n">
         <v>2370</v>
       </c>
-      <c r="C81" t="n">
-        <v>2390</v>
-      </c>
       <c r="D81" t="n">
-        <v>4030</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="82">
@@ -6324,13 +6436,13 @@
         </is>
       </c>
       <c r="B82" t="n">
+        <v>4030</v>
+      </c>
+      <c r="C82" t="n">
         <v>2370</v>
       </c>
-      <c r="C82" t="n">
-        <v>2390</v>
-      </c>
       <c r="D82" t="n">
-        <v>4030</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="83">
@@ -6340,13 +6452,13 @@
         </is>
       </c>
       <c r="B83" t="n">
+        <v>4030</v>
+      </c>
+      <c r="C83" t="n">
         <v>2370</v>
       </c>
-      <c r="C83" t="n">
-        <v>2390</v>
-      </c>
       <c r="D83" t="n">
-        <v>4030</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="84">
@@ -6356,13 +6468,13 @@
         </is>
       </c>
       <c r="B84" t="n">
+        <v>4030</v>
+      </c>
+      <c r="C84" t="n">
         <v>2370</v>
       </c>
-      <c r="C84" t="n">
-        <v>2390</v>
-      </c>
       <c r="D84" t="n">
-        <v>4030</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="85">
@@ -6372,13 +6484,13 @@
         </is>
       </c>
       <c r="B85" t="n">
+        <v>3730</v>
+      </c>
+      <c r="C85" t="n">
         <v>2370</v>
       </c>
-      <c r="C85" t="n">
-        <v>2390</v>
-      </c>
       <c r="D85" t="n">
-        <v>3730</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="86">
@@ -6388,13 +6500,13 @@
         </is>
       </c>
       <c r="B86" t="n">
+        <v>3730</v>
+      </c>
+      <c r="C86" t="n">
         <v>2370</v>
       </c>
-      <c r="C86" t="n">
-        <v>2390</v>
-      </c>
       <c r="D86" t="n">
-        <v>3730</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="87">
@@ -6404,13 +6516,13 @@
         </is>
       </c>
       <c r="B87" t="n">
+        <v>3730</v>
+      </c>
+      <c r="C87" t="n">
         <v>2370</v>
       </c>
-      <c r="C87" t="n">
-        <v>2390</v>
-      </c>
       <c r="D87" t="n">
-        <v>3730</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="88">
@@ -6420,13 +6532,13 @@
         </is>
       </c>
       <c r="B88" t="n">
+        <v>3730</v>
+      </c>
+      <c r="C88" t="n">
         <v>2370</v>
       </c>
-      <c r="C88" t="n">
-        <v>2390</v>
-      </c>
       <c r="D88" t="n">
-        <v>3730</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="89">
@@ -6436,13 +6548,13 @@
         </is>
       </c>
       <c r="B89" t="n">
+        <v>3730</v>
+      </c>
+      <c r="C89" t="n">
         <v>2370</v>
       </c>
-      <c r="C89" t="n">
-        <v>2390</v>
-      </c>
       <c r="D89" t="n">
-        <v>3730</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="90">
@@ -6452,13 +6564,13 @@
         </is>
       </c>
       <c r="B90" t="n">
+        <v>3580</v>
+      </c>
+      <c r="C90" t="n">
         <v>2370</v>
       </c>
-      <c r="C90" t="n">
-        <v>2390</v>
-      </c>
       <c r="D90" t="n">
-        <v>3580</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="91">
@@ -6468,13 +6580,13 @@
         </is>
       </c>
       <c r="B91" t="n">
+        <v>3580</v>
+      </c>
+      <c r="C91" t="n">
         <v>2370</v>
       </c>
-      <c r="C91" t="n">
-        <v>2390</v>
-      </c>
       <c r="D91" t="n">
-        <v>3580</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="92">
@@ -6484,13 +6596,13 @@
         </is>
       </c>
       <c r="B92" t="n">
+        <v>3580</v>
+      </c>
+      <c r="C92" t="n">
         <v>2347</v>
       </c>
-      <c r="C92" t="n">
-        <v>2390</v>
-      </c>
       <c r="D92" t="n">
-        <v>3580</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="93">
@@ -6500,13 +6612,13 @@
         </is>
       </c>
       <c r="B93" t="n">
+        <v>3580</v>
+      </c>
+      <c r="C93" t="n">
         <v>2347</v>
       </c>
-      <c r="C93" t="n">
-        <v>2390</v>
-      </c>
       <c r="D93" t="n">
-        <v>3580</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="94">
@@ -6516,13 +6628,13 @@
         </is>
       </c>
       <c r="B94" t="n">
+        <v>3669</v>
+      </c>
+      <c r="C94" t="n">
         <v>2347</v>
       </c>
-      <c r="C94" t="n">
-        <v>2390</v>
-      </c>
       <c r="D94" t="n">
-        <v>3669</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="95">
@@ -6532,13 +6644,13 @@
         </is>
       </c>
       <c r="B95" t="n">
+        <v>3760</v>
+      </c>
+      <c r="C95" t="n">
         <v>2347</v>
       </c>
-      <c r="C95" t="n">
-        <v>2390</v>
-      </c>
       <c r="D95" t="n">
-        <v>3760</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="96">
@@ -6548,13 +6660,13 @@
         </is>
       </c>
       <c r="B96" t="n">
+        <v>3760</v>
+      </c>
+      <c r="C96" t="n">
         <v>2347</v>
       </c>
-      <c r="C96" t="n">
-        <v>2390</v>
-      </c>
       <c r="D96" t="n">
-        <v>3760</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="97">
@@ -6564,13 +6676,13 @@
         </is>
       </c>
       <c r="B97" t="n">
+        <v>3760</v>
+      </c>
+      <c r="C97" t="n">
         <v>2347</v>
       </c>
-      <c r="C97" t="n">
-        <v>2390</v>
-      </c>
       <c r="D97" t="n">
-        <v>3760</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="98">
@@ -6580,13 +6692,13 @@
         </is>
       </c>
       <c r="B98" t="n">
+        <v>3760</v>
+      </c>
+      <c r="C98" t="n">
         <v>2347</v>
       </c>
-      <c r="C98" t="n">
-        <v>2390</v>
-      </c>
       <c r="D98" t="n">
-        <v>3760</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="99">
@@ -6596,13 +6708,13 @@
         </is>
       </c>
       <c r="B99" t="n">
+        <v>3850</v>
+      </c>
+      <c r="C99" t="n">
         <v>2347</v>
       </c>
-      <c r="C99" t="n">
-        <v>2390</v>
-      </c>
       <c r="D99" t="n">
-        <v>3850</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="100">
@@ -6612,13 +6724,13 @@
         </is>
       </c>
       <c r="B100" t="n">
+        <v>3850</v>
+      </c>
+      <c r="C100" t="n">
         <v>2347</v>
       </c>
-      <c r="C100" t="n">
-        <v>2390</v>
-      </c>
       <c r="D100" t="n">
-        <v>3850</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="101">
@@ -6628,13 +6740,13 @@
         </is>
       </c>
       <c r="B101" t="n">
+        <v>3882</v>
+      </c>
+      <c r="C101" t="n">
         <v>2347</v>
       </c>
-      <c r="C101" t="n">
-        <v>2390</v>
-      </c>
       <c r="D101" t="n">
-        <v>3882</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="102">
@@ -6644,13 +6756,13 @@
         </is>
       </c>
       <c r="B102" t="n">
+        <v>3882</v>
+      </c>
+      <c r="C102" t="n">
         <v>2347</v>
       </c>
-      <c r="C102" t="n">
-        <v>2390</v>
-      </c>
       <c r="D102" t="n">
-        <v>3882</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="103">
@@ -6660,13 +6772,13 @@
         </is>
       </c>
       <c r="B103" t="n">
+        <v>3882</v>
+      </c>
+      <c r="C103" t="n">
         <v>2347</v>
       </c>
-      <c r="C103" t="n">
-        <v>2390</v>
-      </c>
       <c r="D103" t="n">
-        <v>3882</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="104">
@@ -6676,13 +6788,13 @@
         </is>
       </c>
       <c r="B104" t="n">
+        <v>3850</v>
+      </c>
+      <c r="C104" t="n">
         <v>2347</v>
       </c>
-      <c r="C104" t="n">
-        <v>2390</v>
-      </c>
       <c r="D104" t="n">
-        <v>3850</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="105">
@@ -6692,13 +6804,13 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>2345</v>
+        <v>3490</v>
       </c>
       <c r="C105" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D105" t="n">
-        <v>3490</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="106">
@@ -6708,13 +6820,13 @@
         </is>
       </c>
       <c r="B106" t="n">
+        <v>3850</v>
+      </c>
+      <c r="C106" t="n">
         <v>2347</v>
       </c>
-      <c r="C106" t="n">
-        <v>2390</v>
-      </c>
       <c r="D106" t="n">
-        <v>3850</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="107">
@@ -6724,13 +6836,13 @@
         </is>
       </c>
       <c r="B107" t="n">
+        <v>3850</v>
+      </c>
+      <c r="C107" t="n">
         <v>2347</v>
       </c>
-      <c r="C107" t="n">
-        <v>2390</v>
-      </c>
       <c r="D107" t="n">
-        <v>3850</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="108">
@@ -6740,13 +6852,13 @@
         </is>
       </c>
       <c r="B108" t="n">
+        <v>3850</v>
+      </c>
+      <c r="C108" t="n">
         <v>2347</v>
       </c>
-      <c r="C108" t="n">
-        <v>2390</v>
-      </c>
       <c r="D108" t="n">
-        <v>3850</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="109">
@@ -6756,13 +6868,13 @@
         </is>
       </c>
       <c r="B109" t="n">
+        <v>3850</v>
+      </c>
+      <c r="C109" t="n">
         <v>2347</v>
       </c>
-      <c r="C109" t="n">
-        <v>2390</v>
-      </c>
       <c r="D109" t="n">
-        <v>3850</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="110">
@@ -6772,13 +6884,13 @@
         </is>
       </c>
       <c r="B110" t="n">
+        <v>3850</v>
+      </c>
+      <c r="C110" t="n">
         <v>2347</v>
       </c>
-      <c r="C110" t="n">
-        <v>2390</v>
-      </c>
       <c r="D110" t="n">
-        <v>3850</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="111">
@@ -6788,13 +6900,13 @@
         </is>
       </c>
       <c r="B111" t="n">
+        <v>3850</v>
+      </c>
+      <c r="C111" t="n">
         <v>2347</v>
       </c>
-      <c r="C111" t="n">
-        <v>2390</v>
-      </c>
       <c r="D111" t="n">
-        <v>3850</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="112">
@@ -6804,13 +6916,13 @@
         </is>
       </c>
       <c r="B112" t="n">
+        <v>3850</v>
+      </c>
+      <c r="C112" t="n">
         <v>2347</v>
       </c>
-      <c r="C112" t="n">
-        <v>2390</v>
-      </c>
       <c r="D112" t="n">
-        <v>3850</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="113">
@@ -6820,13 +6932,13 @@
         </is>
       </c>
       <c r="B113" t="n">
+        <v>3850</v>
+      </c>
+      <c r="C113" t="n">
         <v>2347</v>
       </c>
-      <c r="C113" t="n">
-        <v>2390</v>
-      </c>
       <c r="D113" t="n">
-        <v>3850</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="114">
@@ -6836,13 +6948,13 @@
         </is>
       </c>
       <c r="B114" t="n">
+        <v>3850</v>
+      </c>
+      <c r="C114" t="n">
         <v>2347</v>
       </c>
-      <c r="C114" t="n">
-        <v>2390</v>
-      </c>
       <c r="D114" t="n">
-        <v>3850</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="115">
@@ -6852,13 +6964,13 @@
         </is>
       </c>
       <c r="B115" t="n">
+        <v>3850</v>
+      </c>
+      <c r="C115" t="n">
         <v>2347</v>
       </c>
-      <c r="C115" t="n">
-        <v>2390</v>
-      </c>
       <c r="D115" t="n">
-        <v>3850</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="116">
@@ -6868,13 +6980,13 @@
         </is>
       </c>
       <c r="B116" t="n">
+        <v>3850</v>
+      </c>
+      <c r="C116" t="n">
         <v>2347</v>
       </c>
-      <c r="C116" t="n">
-        <v>2390</v>
-      </c>
       <c r="D116" t="n">
-        <v>3850</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="117">
@@ -6884,13 +6996,13 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>2345</v>
+        <v>3700</v>
       </c>
       <c r="C117" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D117" t="n">
-        <v>3700</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="118">
@@ -6900,13 +7012,13 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>2345</v>
+        <v>3700</v>
       </c>
       <c r="C118" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D118" t="n">
-        <v>3700</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="119">
@@ -6916,13 +7028,13 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>2345</v>
+        <v>3700</v>
       </c>
       <c r="C119" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D119" t="n">
-        <v>3700</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="120">
@@ -6932,13 +7044,13 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>2345</v>
+        <v>3700</v>
       </c>
       <c r="C120" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D120" t="n">
-        <v>3700</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="121">
@@ -6948,13 +7060,13 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>2345</v>
+        <v>3490</v>
       </c>
       <c r="C121" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D121" t="n">
-        <v>3490</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="122">
@@ -6964,13 +7076,13 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>2345</v>
+        <v>3490</v>
       </c>
       <c r="C122" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D122" t="n">
-        <v>3490</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="123">
@@ -6980,13 +7092,13 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>2345</v>
+        <v>3490</v>
       </c>
       <c r="C123" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D123" t="n">
-        <v>3490</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="124">
@@ -6996,13 +7108,13 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>2345</v>
+        <v>3490</v>
       </c>
       <c r="C124" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D124" t="n">
-        <v>3490</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="125">
@@ -7012,13 +7124,13 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>2345</v>
+        <v>3490</v>
       </c>
       <c r="C125" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D125" t="n">
-        <v>3490</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="126">
@@ -7028,13 +7140,13 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>2345</v>
+        <v>3490</v>
       </c>
       <c r="C126" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D126" t="n">
-        <v>3490</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="127">
@@ -7044,13 +7156,13 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>2345</v>
+        <v>3490</v>
       </c>
       <c r="C127" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D127" t="n">
-        <v>3490</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="128">
@@ -7060,13 +7172,13 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>2345</v>
+        <v>3490</v>
       </c>
       <c r="C128" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D128" t="n">
-        <v>3490</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="129">
@@ -7076,13 +7188,13 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>2345</v>
+        <v>3490</v>
       </c>
       <c r="C129" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D129" t="n">
-        <v>3490</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="130">
@@ -7092,13 +7204,13 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>2345</v>
+        <v>3490</v>
       </c>
       <c r="C130" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D130" t="n">
-        <v>3490</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="131">
@@ -7108,13 +7220,13 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>2345</v>
+        <v>3490</v>
       </c>
       <c r="C131" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D131" t="n">
-        <v>3490</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="132">
@@ -7124,13 +7236,13 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>2345</v>
+        <v>3490</v>
       </c>
       <c r="C132" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D132" t="n">
-        <v>3490</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="133">
@@ -7140,13 +7252,13 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>2345</v>
+        <v>3490</v>
       </c>
       <c r="C133" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D133" t="n">
-        <v>3490</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="134">
@@ -7156,13 +7268,13 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>2345</v>
+        <v>3490</v>
       </c>
       <c r="C134" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D134" t="n">
-        <v>3490</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="135">
@@ -7172,13 +7284,13 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>2345</v>
+        <v>3490</v>
       </c>
       <c r="C135" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D135" t="n">
-        <v>3490</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="136">
@@ -7188,13 +7300,13 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>2345</v>
+        <v>3490</v>
       </c>
       <c r="C136" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D136" t="n">
-        <v>3490</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="137">
@@ -7204,13 +7316,13 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>2345</v>
+        <v>3490</v>
       </c>
       <c r="C137" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D137" t="n">
-        <v>3490</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="138">
@@ -7220,13 +7332,13 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>2345</v>
+        <v>3490</v>
       </c>
       <c r="C138" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D138" t="n">
-        <v>3490</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="139">
@@ -7236,13 +7348,13 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>2345</v>
+        <v>3490</v>
       </c>
       <c r="C139" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D139" t="n">
-        <v>3490</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="140">
@@ -7252,13 +7364,13 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>2345</v>
+        <v>3490</v>
       </c>
       <c r="C140" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D140" t="n">
-        <v>3490</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="141">
@@ -7268,13 +7380,13 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>2345</v>
+        <v>3490</v>
       </c>
       <c r="C141" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D141" t="n">
-        <v>3490</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="142">
@@ -7284,13 +7396,13 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>2345</v>
+        <v>3490</v>
       </c>
       <c r="C142" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D142" t="n">
-        <v>3490</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="143">
@@ -7300,13 +7412,13 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>2345</v>
+        <v>3690</v>
       </c>
       <c r="C143" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D143" t="n">
-        <v>3690</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="144">
@@ -7316,13 +7428,13 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>2345</v>
+        <v>3690</v>
       </c>
       <c r="C144" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D144" t="n">
-        <v>3690</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="145">
@@ -7332,13 +7444,13 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>2345</v>
+        <v>3690</v>
       </c>
       <c r="C145" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D145" t="n">
-        <v>3690</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="146">
@@ -7348,13 +7460,13 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>2345</v>
+        <v>3690</v>
       </c>
       <c r="C146" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D146" t="n">
-        <v>3690</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="147">
@@ -7364,13 +7476,13 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>2345</v>
+        <v>3789</v>
       </c>
       <c r="C147" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D147" t="n">
-        <v>3789</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="148">
@@ -7380,13 +7492,13 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>2345</v>
+        <v>3690</v>
       </c>
       <c r="C148" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D148" t="n">
-        <v>3690</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="149">
@@ -7396,13 +7508,13 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>2345</v>
+        <v>3712</v>
       </c>
       <c r="C149" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D149" t="n">
-        <v>3712</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="150">
@@ -7412,13 +7524,13 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>2345</v>
+        <v>3890</v>
       </c>
       <c r="C150" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D150" t="n">
-        <v>3890</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="151">
@@ -7428,13 +7540,13 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>2345</v>
+        <v>3890</v>
       </c>
       <c r="C151" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D151" t="n">
-        <v>3890</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="152">
@@ -7444,13 +7556,13 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>2345</v>
+        <v>3890</v>
       </c>
       <c r="C152" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D152" t="n">
-        <v>3890</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="153">
@@ -7460,13 +7572,13 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>2345</v>
+        <v>3890</v>
       </c>
       <c r="C153" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D153" t="n">
-        <v>3890</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="154">
@@ -7476,13 +7588,13 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>2345</v>
+        <v>3890</v>
       </c>
       <c r="C154" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D154" t="n">
-        <v>3890</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="155">
@@ -7492,13 +7604,13 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>2345</v>
+        <v>3890</v>
       </c>
       <c r="C155" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D155" t="n">
-        <v>3890</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="156">
@@ -7508,13 +7620,13 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>2345</v>
+        <v>3890</v>
       </c>
       <c r="C156" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D156" t="n">
-        <v>3890</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="157">
@@ -7524,13 +7636,13 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>2345</v>
+        <v>3890</v>
       </c>
       <c r="C157" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D157" t="n">
-        <v>3890</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="158">
@@ -7540,13 +7652,13 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>2345</v>
+        <v>3890</v>
       </c>
       <c r="C158" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D158" t="n">
-        <v>3890</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="159">
@@ -7556,13 +7668,13 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>2345</v>
+        <v>3890</v>
       </c>
       <c r="C159" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D159" t="n">
-        <v>3890</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="160">
@@ -7572,13 +7684,13 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>2345</v>
+        <v>3890</v>
       </c>
       <c r="C160" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D160" t="n">
-        <v>3890</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="161">
@@ -7588,13 +7700,13 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>2345</v>
+        <v>3590</v>
       </c>
       <c r="C161" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D161" t="n">
-        <v>3590</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="162">
@@ -7604,13 +7716,13 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>2345</v>
+        <v>3590</v>
       </c>
       <c r="C162" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D162" t="n">
-        <v>3590</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="163">
@@ -7620,13 +7732,13 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>2345</v>
+        <v>3590</v>
       </c>
       <c r="C163" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D163" t="n">
-        <v>3590</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="164">
@@ -7636,13 +7748,13 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>2345</v>
+        <v>3590</v>
       </c>
       <c r="C164" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D164" t="n">
-        <v>3590</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="165">
@@ -7652,13 +7764,13 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>2345</v>
+        <v>3590</v>
       </c>
       <c r="C165" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D165" t="n">
-        <v>3590</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="166">
@@ -7668,13 +7780,13 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>2345</v>
+        <v>3590</v>
       </c>
       <c r="C166" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D166" t="n">
-        <v>3590</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="167">
@@ -7684,13 +7796,13 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>2345</v>
+        <v>3590</v>
       </c>
       <c r="C167" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D167" t="n">
-        <v>3590</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="168">
@@ -7700,13 +7812,13 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>2345</v>
+        <v>3590</v>
       </c>
       <c r="C168" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D168" t="n">
-        <v>3590</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="169">
@@ -7716,13 +7828,13 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>2345</v>
+        <v>3590</v>
       </c>
       <c r="C169" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D169" t="n">
-        <v>3590</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="170">
@@ -7732,13 +7844,13 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>2345</v>
+        <v>3590</v>
       </c>
       <c r="C170" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D170" t="n">
-        <v>3590</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="171">
@@ -7748,13 +7860,13 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>2345</v>
+        <v>3590</v>
       </c>
       <c r="C171" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D171" t="n">
-        <v>3590</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="172">
@@ -7764,13 +7876,13 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>2345</v>
+        <v>3590</v>
       </c>
       <c r="C172" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D172" t="n">
-        <v>3590</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="173">
@@ -7780,13 +7892,13 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>2345</v>
+        <v>3590</v>
       </c>
       <c r="C173" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D173" t="n">
-        <v>3590</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="174">
@@ -7796,13 +7908,13 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>2345</v>
+        <v>3390</v>
       </c>
       <c r="C174" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D174" t="n">
-        <v>3390</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="175">
@@ -7812,13 +7924,13 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>2345</v>
+        <v>3390</v>
       </c>
       <c r="C175" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D175" t="n">
-        <v>3390</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="176">
@@ -7828,13 +7940,13 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>2345</v>
+        <v>3390</v>
       </c>
       <c r="C176" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D176" t="n">
-        <v>3390</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="177">
@@ -7844,13 +7956,13 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>2345</v>
+        <v>3390</v>
       </c>
       <c r="C177" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D177" t="n">
-        <v>3390</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="178">
@@ -7860,13 +7972,13 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>2345</v>
+        <v>3390</v>
       </c>
       <c r="C178" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D178" t="n">
-        <v>3390</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="179">
@@ -7876,13 +7988,13 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>2345</v>
+        <v>3390</v>
       </c>
       <c r="C179" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D179" t="n">
-        <v>3390</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="180">
@@ -7892,13 +8004,13 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>2345</v>
+        <v>3390</v>
       </c>
       <c r="C180" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D180" t="n">
-        <v>3390</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="181">
@@ -7908,13 +8020,13 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>2345</v>
+        <v>3390</v>
       </c>
       <c r="C181" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D181" t="n">
-        <v>3390</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="182">
@@ -7924,13 +8036,13 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>2345</v>
+        <v>3390</v>
       </c>
       <c r="C182" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D182" t="n">
-        <v>3390</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="183">
@@ -7940,13 +8052,13 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>2345</v>
+        <v>3390</v>
       </c>
       <c r="C183" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D183" t="n">
-        <v>3390</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="184">
@@ -7956,13 +8068,13 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>2345</v>
+        <v>3390</v>
       </c>
       <c r="C184" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D184" t="n">
-        <v>3390</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="185">
@@ -7972,13 +8084,13 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>2345</v>
+        <v>3390</v>
       </c>
       <c r="C185" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D185" t="n">
-        <v>3390</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="186">
@@ -7988,13 +8100,13 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>2345</v>
+        <v>3390</v>
       </c>
       <c r="C186" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D186" t="n">
-        <v>3390</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="187">
@@ -8004,13 +8116,13 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>2345</v>
+        <v>3390</v>
       </c>
       <c r="C187" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D187" t="n">
-        <v>3390</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="188">
@@ -8020,13 +8132,13 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>2345</v>
+        <v>3390</v>
       </c>
       <c r="C188" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D188" t="n">
-        <v>3390</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="189">
@@ -8036,13 +8148,13 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>2345</v>
+        <v>3390</v>
       </c>
       <c r="C189" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D189" t="n">
-        <v>3390</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="190">
@@ -8052,13 +8164,13 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>2345</v>
+        <v>3390</v>
       </c>
       <c r="C190" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D190" t="n">
-        <v>3390</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="191">
@@ -8068,13 +8180,13 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>2345</v>
+        <v>3390</v>
       </c>
       <c r="C191" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D191" t="n">
-        <v>3390</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="192">
@@ -8084,13 +8196,13 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C192" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D192" t="n">
-        <v>3140</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="193">
@@ -8100,13 +8212,13 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C193" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D193" t="n">
-        <v>3140</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="194">
@@ -8116,13 +8228,13 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C194" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D194" t="n">
-        <v>3140</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="195">
@@ -8132,13 +8244,13 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C195" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D195" t="n">
-        <v>3140</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="196">
@@ -8148,13 +8260,13 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C196" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D196" t="n">
-        <v>3140</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="197">
@@ -8164,13 +8276,13 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C197" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D197" t="n">
-        <v>3140</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="198">
@@ -8180,13 +8292,13 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C198" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D198" t="n">
-        <v>3140</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="199">
@@ -8196,13 +8308,13 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C199" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D199" t="n">
-        <v>3140</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="200">
@@ -8212,13 +8324,13 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C200" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D200" t="n">
-        <v>3140</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="201">
@@ -8228,13 +8340,13 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C201" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D201" t="n">
-        <v>3140</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="202">
@@ -8244,13 +8356,13 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C202" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D202" t="n">
-        <v>3140</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="203">
@@ -8260,13 +8372,13 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C203" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D203" t="n">
-        <v>3140</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="204">
@@ -8276,13 +8388,13 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C204" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D204" t="n">
-        <v>3140</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="205">
@@ -8292,13 +8404,13 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C205" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D205" t="n">
-        <v>3140</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="206">
@@ -8308,13 +8420,13 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C206" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D206" t="n">
-        <v>3140</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="207">
@@ -8324,13 +8436,13 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C207" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D207" t="n">
-        <v>3140</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="208">
@@ -8340,13 +8452,13 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C208" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D208" t="n">
-        <v>3140</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="209">
@@ -8356,13 +8468,13 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C209" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D209" t="n">
-        <v>3140</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="210">
@@ -8372,13 +8484,13 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C210" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D210" t="n">
-        <v>3140</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="211">
@@ -8388,13 +8500,13 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C211" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D211" t="n">
-        <v>3140</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="212">
@@ -8404,13 +8516,13 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C212" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D212" t="n">
-        <v>3140</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="213">
@@ -8420,13 +8532,13 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C213" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D213" t="n">
-        <v>3140</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="214">
@@ -8436,13 +8548,13 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C214" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D214" t="n">
-        <v>3140</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="215">
@@ -8452,13 +8564,13 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C215" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D215" t="n">
-        <v>3140</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="216">
@@ -8468,13 +8580,13 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C216" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D216" t="n">
-        <v>3140</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="217">
@@ -8484,13 +8596,13 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C217" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D217" t="n">
-        <v>3140</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="218">
@@ -8500,13 +8612,13 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C218" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D218" t="n">
-        <v>3140</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="219">
@@ -8516,13 +8628,13 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C219" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D219" t="n">
-        <v>3140</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="220">
@@ -8532,13 +8644,13 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C220" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D220" t="n">
-        <v>3140</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="221">
@@ -8548,13 +8660,13 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C221" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D221" t="n">
-        <v>3140</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="222">
@@ -8564,13 +8676,13 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C222" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D222" t="n">
-        <v>3140</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="223">
@@ -8580,13 +8692,13 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C223" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D223" t="n">
-        <v>3140</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="224">
@@ -8596,13 +8708,13 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C224" t="n">
-        <v>2390</v>
+        <v>2345</v>
       </c>
       <c r="D224" t="n">
-        <v>3140</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="225">
@@ -8612,13 +8724,13 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>2345</v>
+        <v>2940</v>
       </c>
       <c r="C225" t="n">
-        <v>2590</v>
+        <v>2345</v>
       </c>
       <c r="D225" t="n">
-        <v>2940</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="226">
@@ -8628,13 +8740,13 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>2345</v>
+        <v>2940</v>
       </c>
       <c r="C226" t="n">
-        <v>2590</v>
+        <v>2345</v>
       </c>
       <c r="D226" t="n">
-        <v>2940</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="227">
@@ -8644,13 +8756,13 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>2345</v>
+        <v>2940</v>
       </c>
       <c r="C227" t="n">
-        <v>2590</v>
+        <v>2345</v>
       </c>
       <c r="D227" t="n">
-        <v>2940</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="228">
@@ -8660,13 +8772,13 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>2345</v>
+        <v>2940</v>
       </c>
       <c r="C228" t="n">
-        <v>2590</v>
+        <v>2345</v>
       </c>
       <c r="D228" t="n">
-        <v>2940</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="229">
@@ -8676,13 +8788,13 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>2345</v>
+        <v>2940</v>
       </c>
       <c r="C229" t="n">
-        <v>2590</v>
+        <v>2345</v>
       </c>
       <c r="D229" t="n">
-        <v>2940</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="230">
@@ -8692,13 +8804,13 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>2345</v>
+        <v>2940</v>
       </c>
       <c r="C230" t="n">
-        <v>2590</v>
+        <v>2345</v>
       </c>
       <c r="D230" t="n">
-        <v>2940</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="231">
@@ -8708,13 +8820,13 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>2345</v>
+        <v>2940</v>
       </c>
       <c r="C231" t="n">
-        <v>2590</v>
+        <v>2345</v>
       </c>
       <c r="D231" t="n">
-        <v>2940</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="232">
@@ -8724,13 +8836,13 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>2345</v>
+        <v>2940</v>
       </c>
       <c r="C232" t="n">
-        <v>2590</v>
+        <v>2345</v>
       </c>
       <c r="D232" t="n">
-        <v>2940</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="233">
@@ -8740,13 +8852,13 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>2345</v>
+        <v>2940</v>
       </c>
       <c r="C233" t="n">
-        <v>2590</v>
+        <v>2345</v>
       </c>
       <c r="D233" t="n">
-        <v>2940</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="234">
@@ -8756,13 +8868,13 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>2345</v>
+        <v>2965</v>
       </c>
       <c r="C234" t="n">
-        <v>2590</v>
+        <v>2345</v>
       </c>
       <c r="D234" t="n">
-        <v>2965</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="235">
@@ -8772,13 +8884,13 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>2345</v>
+        <v>2990</v>
       </c>
       <c r="C235" t="n">
-        <v>2590</v>
+        <v>2345</v>
       </c>
       <c r="D235" t="n">
-        <v>2990</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="236">
@@ -8788,13 +8900,13 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>2345</v>
+        <v>2990</v>
       </c>
       <c r="C236" t="n">
-        <v>2590</v>
+        <v>2345</v>
       </c>
       <c r="D236" t="n">
-        <v>2990</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="237">
@@ -8804,13 +8916,13 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>2345</v>
+        <v>2990</v>
       </c>
       <c r="C237" t="n">
-        <v>2590</v>
+        <v>2345</v>
       </c>
       <c r="D237" t="n">
-        <v>2990</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="238">
@@ -8820,13 +8932,13 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>2345</v>
+        <v>2940</v>
       </c>
       <c r="C238" t="n">
-        <v>2590</v>
+        <v>2345</v>
       </c>
       <c r="D238" t="n">
-        <v>2940</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="239">
@@ -8836,13 +8948,13 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>2345</v>
+        <v>2940</v>
       </c>
       <c r="C239" t="n">
-        <v>2590</v>
+        <v>2345</v>
       </c>
       <c r="D239" t="n">
-        <v>2940</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="240">
@@ -8852,13 +8964,13 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>2345</v>
+        <v>2940</v>
       </c>
       <c r="C240" t="n">
-        <v>2590</v>
+        <v>2345</v>
       </c>
       <c r="D240" t="n">
-        <v>2940</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="241">
@@ -8868,13 +8980,13 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>2345</v>
+        <v>2940</v>
       </c>
       <c r="C241" t="n">
-        <v>2590</v>
+        <v>2345</v>
       </c>
       <c r="D241" t="n">
-        <v>2940</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="242">
@@ -8884,13 +8996,13 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>2345</v>
+        <v>2940</v>
       </c>
       <c r="C242" t="n">
-        <v>2590</v>
+        <v>2345</v>
       </c>
       <c r="D242" t="n">
-        <v>2940</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="243">
@@ -8900,13 +9012,13 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>2345</v>
+        <v>2940</v>
       </c>
       <c r="C243" t="n">
-        <v>2590</v>
+        <v>2345</v>
       </c>
       <c r="D243" t="n">
-        <v>2940</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="244">
@@ -8916,13 +9028,13 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>2345</v>
+        <v>2940</v>
       </c>
       <c r="C244" t="n">
-        <v>2590</v>
+        <v>2345</v>
       </c>
       <c r="D244" t="n">
-        <v>2940</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="245">
@@ -8932,13 +9044,13 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>2345</v>
+        <v>2940</v>
       </c>
       <c r="C245" t="n">
-        <v>2590</v>
+        <v>2345</v>
       </c>
       <c r="D245" t="n">
-        <v>2940</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="246">
@@ -8948,13 +9060,13 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>2345</v>
+        <v>3014</v>
       </c>
       <c r="C246" t="n">
-        <v>2590</v>
+        <v>2345</v>
       </c>
       <c r="D246" t="n">
-        <v>3014</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="247">
@@ -8964,13 +9076,13 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>2345</v>
+        <v>3014</v>
       </c>
       <c r="C247" t="n">
-        <v>2590</v>
+        <v>2345</v>
       </c>
       <c r="D247" t="n">
-        <v>3014</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="248">
@@ -8980,13 +9092,13 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>2345</v>
+        <v>3038</v>
       </c>
       <c r="C248" t="n">
-        <v>2590</v>
+        <v>2345</v>
       </c>
       <c r="D248" t="n">
-        <v>3038</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="249">
@@ -8996,13 +9108,13 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C249" t="n">
-        <v>2590</v>
+        <v>2345</v>
       </c>
       <c r="D249" t="n">
-        <v>3140</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="250">
@@ -9012,13 +9124,13 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C250" t="n">
-        <v>2590</v>
+        <v>2345</v>
       </c>
       <c r="D250" t="n">
-        <v>3140</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="251">
@@ -9028,13 +9140,13 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C251" t="n">
-        <v>2590</v>
+        <v>2345</v>
       </c>
       <c r="D251" t="n">
-        <v>3140</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="252">
@@ -9044,13 +9156,13 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C252" t="n">
-        <v>2590</v>
+        <v>2345</v>
       </c>
       <c r="D252" t="n">
-        <v>3140</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="253">
@@ -9060,13 +9172,13 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C253" t="n">
-        <v>2590</v>
+        <v>2345</v>
       </c>
       <c r="D253" t="n">
-        <v>3140</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="254">
@@ -9076,13 +9188,13 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C254" t="n">
-        <v>2590</v>
+        <v>2345</v>
       </c>
       <c r="D254" t="n">
-        <v>3140</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="255">
@@ -9092,13 +9204,13 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C255" t="n">
-        <v>2590</v>
+        <v>2345</v>
       </c>
       <c r="D255" t="n">
-        <v>3140</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="256">
@@ -9108,13 +9220,13 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C256" t="n">
-        <v>2590</v>
+        <v>2345</v>
       </c>
       <c r="D256" t="n">
-        <v>3140</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="257">
@@ -9124,13 +9236,13 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C257" t="n">
-        <v>2590</v>
+        <v>2345</v>
       </c>
       <c r="D257" t="n">
-        <v>3140</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="258">
@@ -9140,13 +9252,13 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C258" t="n">
-        <v>2590</v>
+        <v>2345</v>
       </c>
       <c r="D258" t="n">
-        <v>3140</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="259">
@@ -9156,13 +9268,13 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C259" t="n">
-        <v>2590</v>
+        <v>2345</v>
       </c>
       <c r="D259" t="n">
-        <v>3140</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="260">
@@ -9172,13 +9284,13 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C260" t="n">
-        <v>2590</v>
+        <v>2345</v>
       </c>
       <c r="D260" t="n">
-        <v>3140</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="261">
@@ -9188,13 +9300,13 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C261" t="n">
-        <v>2590</v>
+        <v>2345</v>
       </c>
       <c r="D261" t="n">
-        <v>3140</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="262">
@@ -9204,13 +9316,13 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C262" t="n">
-        <v>2590</v>
+        <v>2345</v>
       </c>
       <c r="D262" t="n">
-        <v>3140</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="263">
@@ -9220,13 +9332,13 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C263" t="n">
-        <v>2590</v>
+        <v>2345</v>
       </c>
       <c r="D263" t="n">
-        <v>3140</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="264">
@@ -9236,13 +9348,13 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C264" t="n">
-        <v>2590</v>
+        <v>2345</v>
       </c>
       <c r="D264" t="n">
-        <v>3140</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="265">
@@ -9252,13 +9364,13 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C265" t="n">
-        <v>2590</v>
+        <v>2345</v>
       </c>
       <c r="D265" t="n">
-        <v>3140</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="266">
@@ -9268,13 +9380,13 @@
         </is>
       </c>
       <c r="B266" t="n">
-        <v>2345</v>
+        <v>3140</v>
       </c>
       <c r="C266" t="n">
-        <v>2590</v>
+        <v>2345</v>
       </c>
       <c r="D266" t="n">
-        <v>3140</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="267">
@@ -9284,13 +9396,13 @@
         </is>
       </c>
       <c r="B267" t="n">
-        <v>2345</v>
+        <v>3447</v>
       </c>
       <c r="C267" t="n">
-        <v>2590</v>
+        <v>2345</v>
       </c>
       <c r="D267" t="n">
-        <v>3447</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="268">
@@ -9299,12 +9411,12 @@
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="B268" t="inlineStr"/>
-      <c r="C268" t="n">
-        <v>2590</v>
-      </c>
+      <c r="B268" t="n">
+        <v>3987</v>
+      </c>
+      <c r="C268" t="inlineStr"/>
       <c r="D268" t="n">
-        <v>3987</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="269">
@@ -9313,12 +9425,12 @@
           <t>2026-04-13</t>
         </is>
       </c>
-      <c r="B269" t="inlineStr"/>
-      <c r="C269" t="n">
-        <v>2590</v>
-      </c>
+      <c r="B269" t="n">
+        <v>4335</v>
+      </c>
+      <c r="C269" t="inlineStr"/>
       <c r="D269" t="n">
-        <v>4335</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="270">
@@ -9327,12 +9439,12 @@
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B270" t="inlineStr"/>
-      <c r="C270" t="n">
-        <v>2590</v>
-      </c>
+      <c r="B270" t="n">
+        <v>4335</v>
+      </c>
+      <c r="C270" t="inlineStr"/>
       <c r="D270" t="n">
-        <v>4335</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="271">
@@ -9341,12 +9453,12 @@
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B271" t="inlineStr"/>
-      <c r="C271" t="n">
-        <v>2590</v>
-      </c>
+      <c r="B271" t="n">
+        <v>4335</v>
+      </c>
+      <c r="C271" t="inlineStr"/>
       <c r="D271" t="n">
-        <v>4335</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="272">
@@ -9355,12 +9467,12 @@
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="B272" t="inlineStr"/>
-      <c r="C272" t="n">
-        <v>2590</v>
-      </c>
+      <c r="B272" t="n">
+        <v>4335</v>
+      </c>
+      <c r="C272" t="inlineStr"/>
       <c r="D272" t="n">
-        <v>4335</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="273">
@@ -9369,12 +9481,12 @@
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="B273" t="inlineStr"/>
-      <c r="C273" t="n">
-        <v>2590</v>
-      </c>
+      <c r="B273" t="n">
+        <v>4335</v>
+      </c>
+      <c r="C273" t="inlineStr"/>
       <c r="D273" t="n">
-        <v>4335</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="274">
@@ -9383,12 +9495,12 @@
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="B274" t="inlineStr"/>
-      <c r="C274" t="n">
-        <v>2590</v>
-      </c>
+      <c r="B274" t="n">
+        <v>4335</v>
+      </c>
+      <c r="C274" t="inlineStr"/>
       <c r="D274" t="n">
-        <v>4335</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="275">
@@ -9397,12 +9509,12 @@
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="B275" t="inlineStr"/>
-      <c r="C275" t="n">
-        <v>2590</v>
-      </c>
+      <c r="B275" t="n">
+        <v>4335</v>
+      </c>
+      <c r="C275" t="inlineStr"/>
       <c r="D275" t="n">
-        <v>4335</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="276">
@@ -9411,12 +9523,12 @@
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="B276" t="inlineStr"/>
-      <c r="C276" t="n">
-        <v>2590</v>
-      </c>
+      <c r="B276" t="n">
+        <v>4335</v>
+      </c>
+      <c r="C276" t="inlineStr"/>
       <c r="D276" t="n">
-        <v>4335</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="277">
@@ -9425,12 +9537,12 @@
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="B277" t="inlineStr"/>
-      <c r="C277" t="n">
-        <v>2590</v>
-      </c>
+      <c r="B277" t="n">
+        <v>4335</v>
+      </c>
+      <c r="C277" t="inlineStr"/>
       <c r="D277" t="n">
-        <v>4335</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="278">
@@ -9439,12 +9551,12 @@
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="B278" t="inlineStr"/>
-      <c r="C278" t="n">
-        <v>2590</v>
-      </c>
+      <c r="B278" t="n">
+        <v>4335</v>
+      </c>
+      <c r="C278" t="inlineStr"/>
       <c r="D278" t="n">
-        <v>4335</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="279">
@@ -9453,12 +9565,12 @@
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B279" t="inlineStr"/>
-      <c r="C279" t="n">
-        <v>2590</v>
-      </c>
+      <c r="B279" t="n">
+        <v>4335</v>
+      </c>
+      <c r="C279" t="inlineStr"/>
       <c r="D279" t="n">
-        <v>4335</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="280">
@@ -9467,12 +9579,12 @@
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="B280" t="inlineStr"/>
-      <c r="C280" t="n">
-        <v>2590</v>
-      </c>
+      <c r="B280" t="n">
+        <v>4335</v>
+      </c>
+      <c r="C280" t="inlineStr"/>
       <c r="D280" t="n">
-        <v>4335</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="281">
@@ -9481,12 +9593,12 @@
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="B281" t="inlineStr"/>
-      <c r="C281" t="n">
-        <v>2590</v>
-      </c>
+      <c r="B281" t="n">
+        <v>4335</v>
+      </c>
+      <c r="C281" t="inlineStr"/>
       <c r="D281" t="n">
-        <v>4335</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="282">
@@ -9495,12 +9607,12 @@
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="B282" t="inlineStr"/>
-      <c r="C282" t="n">
+      <c r="B282" t="n">
+        <v>4185</v>
+      </c>
+      <c r="C282" t="inlineStr"/>
+      <c r="D282" t="n">
         <v>2840</v>
-      </c>
-      <c r="D282" t="n">
-        <v>4185</v>
       </c>
     </row>
     <row r="283">
@@ -9509,12 +9621,12 @@
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="B283" t="inlineStr"/>
-      <c r="C283" t="n">
+      <c r="B283" t="n">
+        <v>4185</v>
+      </c>
+      <c r="C283" t="inlineStr"/>
+      <c r="D283" t="n">
         <v>2840</v>
-      </c>
-      <c r="D283" t="n">
-        <v>4185</v>
       </c>
     </row>
     <row r="284">
@@ -9523,12 +9635,12 @@
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="B284" t="inlineStr"/>
-      <c r="C284" t="n">
+      <c r="B284" t="n">
+        <v>4185</v>
+      </c>
+      <c r="C284" t="inlineStr"/>
+      <c r="D284" t="n">
         <v>2840</v>
-      </c>
-      <c r="D284" t="n">
-        <v>4185</v>
       </c>
     </row>
     <row r="285">
@@ -9537,12 +9649,12 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="B285" t="inlineStr"/>
-      <c r="C285" t="n">
+      <c r="B285" t="n">
+        <v>4185</v>
+      </c>
+      <c r="C285" t="inlineStr"/>
+      <c r="D285" t="n">
         <v>2840</v>
-      </c>
-      <c r="D285" t="n">
-        <v>4185</v>
       </c>
     </row>
     <row r="286">
@@ -9551,12 +9663,12 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="B286" t="inlineStr"/>
-      <c r="C286" t="n">
+      <c r="B286" t="n">
+        <v>4185</v>
+      </c>
+      <c r="C286" t="inlineStr"/>
+      <c r="D286" t="n">
         <v>3040</v>
-      </c>
-      <c r="D286" t="n">
-        <v>4185</v>
       </c>
     </row>
     <row r="287">
@@ -9565,12 +9677,12 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="B287" t="inlineStr"/>
-      <c r="C287" t="n">
+      <c r="B287" t="n">
+        <v>4185</v>
+      </c>
+      <c r="C287" t="inlineStr"/>
+      <c r="D287" t="n">
         <v>3040</v>
-      </c>
-      <c r="D287" t="n">
-        <v>4185</v>
       </c>
     </row>
     <row r="288">
@@ -9579,12 +9691,124 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="B288" t="inlineStr"/>
-      <c r="C288" t="n">
+      <c r="B288" t="n">
+        <v>4185</v>
+      </c>
+      <c r="C288" t="inlineStr"/>
+      <c r="D288" t="n">
         <v>3040</v>
       </c>
-      <c r="D288" t="n">
-        <v>4185</v>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>4770</v>
+      </c>
+      <c r="C289" t="inlineStr"/>
+      <c r="D289" t="n">
+        <v>3040</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>4770</v>
+      </c>
+      <c r="C290" t="inlineStr"/>
+      <c r="D290" t="n">
+        <v>3040</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>4770</v>
+      </c>
+      <c r="C291" t="inlineStr"/>
+      <c r="D291" t="n">
+        <v>3040</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>4775</v>
+      </c>
+      <c r="C292" t="inlineStr"/>
+      <c r="D292" t="n">
+        <v>3040</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>4775</v>
+      </c>
+      <c r="C293" t="inlineStr"/>
+      <c r="D293" t="n">
+        <v>3040</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>4775</v>
+      </c>
+      <c r="C294" t="inlineStr"/>
+      <c r="D294" t="n">
+        <v>3592</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>4775</v>
+      </c>
+      <c r="C295" t="inlineStr"/>
+      <c r="D295" t="n">
+        <v>3592</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>5700</v>
+      </c>
+      <c r="C296" t="inlineStr"/>
+      <c r="D296" t="n">
+        <v>3592</v>
       </c>
     </row>
   </sheetData>
